--- a/器件仓库.xlsx
+++ b/器件仓库.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PersonalFiles\器件仓库\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PersonalFiles\Electronic_devices_repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E2A865-FFC3-4517-AD65-C11384F1EFA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4445A4F-B3E0-4A0A-9C89-9254590246BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="268">
   <si>
     <t>蜂鸣器</t>
   </si>
@@ -852,6 +852,62 @@
   </si>
   <si>
     <t>10nf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A0062</t>
+  </si>
+  <si>
+    <t>A0063</t>
+  </si>
+  <si>
+    <t>A0064</t>
+  </si>
+  <si>
+    <t>A0065</t>
+  </si>
+  <si>
+    <t>A0066</t>
+  </si>
+  <si>
+    <t>A0067</t>
+  </si>
+  <si>
+    <t>A0068</t>
+  </si>
+  <si>
+    <t>A0069</t>
+  </si>
+  <si>
+    <t>68k 1%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>13欧 1%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>27k 1%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>33欧 1%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>15k 1%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>200k 1%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.7欧 1%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0欧 1%</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1222,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
@@ -3304,6 +3360,166 @@
       </c>
       <c r="G82" s="1">
         <v>50</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G83" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G84" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G85" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G86" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G87" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G88" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G89" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G90" s="1">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
